--- a/data/employees/EMP006/AST-EMP006-06.xlsx
+++ b/data/employees/EMP006/AST-EMP006-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shift Productivity Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,199 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Shift Productivity Report - Avery Wilson (Operations)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Avery Wilson | Role: Specialist | Location: Portland | Date: 2025-01-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>74</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Shift</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Efficiency %</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>87</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>EMP006</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Team Lead A</t>
+          <t>Ast Emp006 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>96</v>
+        <v>78</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>EMP006</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Team Lead B</t>
+          <t>Ast Emp006 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>Mentoring</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G6" t="n">
-        <v>102</v>
+        <v>86</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>EMP006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Team Lead C</t>
+          <t>Ast Emp006 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>92</v>
+        <v>70</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>EMP006</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Team Lead D</t>
+          <t>Ast Emp006 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9200</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9500</v>
-      </c>
-      <c r="G8" t="n">
-        <v>96.8</v>
+        <v>96</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>96</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>68</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>69</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>97</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>76</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>86</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>97</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>95</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>85</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>77</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>75</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>97</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>89</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>74</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>89</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp006 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>67</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP006</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP006 contributes to ast emp006 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>